--- a/DOSSIES_MULTIFORMATO/FAAR_SEDEL/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/FAAR_SEDEL/dossie.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,7 +636,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2020NE00286</t>
+          <t>2020NE00284</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2566.26</v>
+        <v>10204.74</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -655,14 +655,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANULAÇÃO PARCIAL DA NE Nº 055/2020, CONFORME DECRETO Nº 43.042 DE 18 DE NOVEMBRO DE 2020 QUE DISPÕE SOBRE NORMAS E PROCEDIMENTOS PARA O ENCERRAMENTO DA EXECUÇÃO ORÇAMENTÁRIA, FINANCEIRA E CONTÁBIL DE </t>
+          <t>ANULAÇÃO TOTAL DA NE Nº 056/2020 , CONFORME DECRETO Nº 43.042 DE 18 DE NOVEMBRO DE 2020 QUE DISPÕE SOBRE NORMAS E PROCEDIMENTOS PARA O ENCERRAMENTO DA EXECUÇÃO ORÇAMENTÁRIA, FINANCEIRA E CONTÁBIL DE 2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2020NE00284</t>
+          <t>2020NE00286</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10204.74</v>
+        <v>2566.26</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -681,14 +681,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE Nº 056/2020 , CONFORME DECRETO Nº 43.042 DE 18 DE NOVEMBRO DE 2020 QUE DISPÕE SOBRE NORMAS E PROCEDIMENTOS PARA O ENCERRAMENTO DA EXECUÇÃO ORÇAMENTÁRIA, FINANCEIRA E CONTÁBIL DE 2</t>
+          <t xml:space="preserve">ANULAÇÃO PARCIAL DA NE Nº 055/2020, CONFORME DECRETO Nº 43.042 DE 18 DE NOVEMBRO DE 2020 QUE DISPÕE SOBRE NORMAS E PROCEDIMENTOS PARA O ENCERRAMENTO DA EXECUÇÃO ORÇAMENTÁRIA, FINANCEIRA E CONTÁBIL DE </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023NE0000501</t>
+          <t>2024NE0000484</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -698,11 +698,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31/10/2023</t>
+          <t>31/10/2024</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17085.03</v>
+        <v>41105.36</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -718,17 +718,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2022NE0000572</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>2023NE0000501</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>26/2021</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>30/11/2022</t>
+          <t>31/10/2023</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4662.74</v>
+        <v>17085.03</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -737,28 +741,28 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em Serviço de Execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e Folha de Pagamento de Pessoal, processar folhas de pagamento e fornecer relat</t>
+          <t xml:space="preserve">Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta FAAR. PARECER N. 377/2023 – ASSJUR/FAAR PARECER </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023NE0000472</t>
+          <t>2024NE0000265</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3/2020</t>
+          <t>26/2021</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>31/07/2024</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5849.15</v>
+        <v>39593.16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -767,28 +771,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB (SPROWEB). PARECER Nº 143/2023 – ASSJUR/FAAR TC: 0003/2020 AD: 03.</t>
+          <t xml:space="preserve">Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta FAAR. PARECER N. 377/2023 – ASSJUR/FAAR PARECER </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2021NE0000198</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2/2020</t>
-        </is>
-      </c>
+          <t>2022NE0000572</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>30/06/2021</t>
+          <t>30/11/2022</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17681.14</v>
+        <v>4662.74</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -797,24 +797,28 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1º Termo Aditivo ao Contrato 002.2020 - Serviços de infraestrutura de TI, Internet e Metromao</t>
+          <t>Contratação de empresa especializada em Serviço de Execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e Folha de Pagamento de Pessoal, processar folhas de pagamento e fornecer relat</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2021NE0000196</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>2024NE0000475</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>26/2021</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>30/06/2021</t>
+          <t>30/10/2024</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17681.14</v>
+        <v>39593.16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -823,28 +827,28 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anulação total do saldo da Ne nº. 186/21, para ajustes na descrição.</t>
+          <t xml:space="preserve">Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta FAAR. PARECER N. 377/2023 – ASSJUR/FAAR PARECER </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2022NE0000363</t>
+          <t>2023NE0000472</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26/2021</t>
+          <t>3/2020</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>29/08/2022</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>164431.28</v>
+        <v>5849.15</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -853,14 +857,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM INSTALAÇÃO DE LINKS DE INTERNET, PARA QUE POSSA INTERLIGAR NOSSOS ESPAÇOS ESPORTIVOS, DE RESPONSABILIDADE DESTA FUNDAÇÃO.</t>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB (SPROWEB). PARECER Nº 143/2023 – ASSJUR/FAAR TC: 0003/2020 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2021NE0000188</t>
+          <t>2024NE0000318</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -870,11 +874,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>29/06/2021</t>
+          <t>30/09/2024</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4251.98</v>
+        <v>4888.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -883,24 +887,28 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de disponibilização de Gestor de Conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação visual do Governo do Es</t>
+          <t>Contratação de empresa para prestação de serviço de hospedagem do site, compreendendo o armazenamento do site desta FAAR na infraestrutura tecnológica, para atender as necessidades desta FAAR. PARECER</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2021NE0000020</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>2024NE0000317</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2/2020</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>29/01/2021</t>
+          <t>30/09/2024</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5745.6</v>
+        <v>18603.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -909,24 +917,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em Serviço de Execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e Folha de Pagamento de Pessoal, processar folhas de pagamento e fornecer relat</t>
+          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e manutenção, através da Rede Metropolitana de Manaus através de fibra ótica, incluindo o serviço de Acesso à Inter</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023NE0000600</t>
+          <t>2021NE0000196</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>28/12/2023</t>
+          <t>30/06/2021</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1493.82</v>
+        <v>17681.14</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -935,28 +943,28 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para execução do Sistema PRODAMRH - Cadastro e Folha de Pagamento de Pessoal.</t>
+          <t>Anulação total do saldo da Ne nº. 186/21, para ajustes na descrição.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2022NE00279</t>
+          <t>2021NE0000198</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3/2020</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>28/06/2022</t>
+          <t>30/06/2021</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2335.68</v>
+        <v>17681.14</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -965,28 +973,28 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2022</t>
+          <t>1º Termo Aditivo ao Contrato 002.2020 - Serviços de infraestrutura de TI, Internet e Metromao</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2022NE0000281</t>
+          <t>2022NE0000363</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4/2020</t>
+          <t>26/2021</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>28/06/2022</t>
+          <t>29/08/2022</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4880</v>
+        <v>164431.28</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -995,28 +1003,28 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de disponibilização de Gestor de Conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação visual do Governo do Es</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM INSTALAÇÃO DE LINKS DE INTERNET, PARA QUE POSSA INTERLIGAR NOSSOS ESPAÇOS ESPORTIVOS, DE RESPONSABILIDADE DESTA FUNDAÇÃO.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2022NE00281</t>
+          <t>2025NE0000237</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4/2020</t>
+          <t>26/2021</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>28/06/2022</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4880</v>
+        <v>41105.36</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1025,28 +1033,28 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2022</t>
+          <t xml:space="preserve">Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta FAAR. PARECER N. 377/2023 – ASSJUR/FAAR PARECER </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2022NE0000279</t>
+          <t>2021NE0000188</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3/2020</t>
+          <t>4/2020</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>28/06/2022</t>
+          <t>29/06/2021</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2335.68</v>
+        <v>4251.98</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1055,28 +1063,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).</t>
+          <t>Contratação de empresa especializada no serviço de disponibilização de Gestor de Conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação visual do Governo do Es</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2022NE00283</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2/2020</t>
-        </is>
-      </c>
+          <t>2021NE0000020</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>28/06/2022</t>
+          <t>29/01/2021</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>20292.6</v>
+        <v>5745.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1085,28 +1089,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2022</t>
+          <t>Contratação de empresa especializada em Serviço de Execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e Folha de Pagamento de Pessoal, processar folhas de pagamento e fornecer relat</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2022NE0000283</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2/2020</t>
-        </is>
-      </c>
+          <t>2023NE0000600</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>28/06/2022</t>
+          <t>28/12/2023</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20292.6</v>
+        <v>1493.82</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1115,28 +1115,28 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e Manutenção, através da Rede Metropolitana de Manaus REPAM/MetroMao por meio de fibra ótica, incluindo o serviço d</t>
+          <t>Contratação de empresa especializada para execução do Sistema PRODAMRH - Cadastro e Folha de Pagamento de Pessoal.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2021NE00187</t>
+          <t>2025NE0000267</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3/2020</t>
+          <t>7/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>28/06/2021</t>
+          <t>28/08/2025</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2335.68</v>
+        <v>19852.22</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1145,24 +1145,28 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1º Termo Aditivo ao Contrato 003/2020 - SPROWEB</t>
+          <t>Contratação da PRODAM – Processamento de Dados Amazonas S/A, referente a prestação de serviços de METROMAO, incluindo locação de equipamentos e suporte, fornecimento de acesso gerenciado à internet po</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2021NE0000186</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>2022NE0000283</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2/2020</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>28/06/2021</t>
+          <t>28/06/2022</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>17681.14</v>
+        <v>20292.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1178,21 +1182,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2021NE0000187</t>
+          <t>2022NE00283</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3/2020</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>28/06/2021</t>
+          <t>28/06/2022</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2335.68</v>
+        <v>20292.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1201,14 +1205,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).</t>
+          <t>Cobertura Financeira 2022</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2023NE0000469</t>
+          <t>2022NE0000279</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1218,11 +1222,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>27/10/2023</t>
+          <t>28/06/2022</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1167.84</v>
+        <v>2335.68</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1231,28 +1235,28 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB). PARECER Nº 134/2022 – ASSJUR/FAAR TC: 003/2020 AD: 02.</t>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2023NE0000207</t>
+          <t>2022NE00281</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3/2020</t>
+          <t>4/2020</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>27/06/2023</t>
+          <t>28/06/2022</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1169.83</v>
+        <v>4880</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1261,24 +1265,28 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB (SPROWEB). PARECER Nº 143/2023 – ASSJUR/FAAR TC: 0003/2020 AD: 03.</t>
+          <t>Cobertura Financeira 2022</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2021NE0000108</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>2022NE0000281</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>4/2020</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>27/04/2021</t>
+          <t>28/06/2022</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3401.58</v>
+        <v>4880</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1287,24 +1295,28 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">119820 - (ID-119820) HOSPEDAGEM DE SISTEMA DE INFORMAÇÃO, Descrição: Contratação de empresa especializada para prestação de serviço de hospedagem de Website, conforme Projeto Básico. MARCA: sem marca </t>
+          <t>Contratação de empresa especializada no serviço de disponibilização de Gestor de Conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação visual do Governo do Es</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2021NE0000103</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>2022NE00279</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>27/04/2021</t>
+          <t>28/06/2022</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>17967.2</v>
+        <v>2335.68</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1313,24 +1325,28 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">115752 - (ID-115752) SERVIÇO DE TRANSMISSÃO DE DADOS, Descrição: Contratação de empresa especializada para fornecimento de circuito de transmissão de dados para conexão cliente/fornecedor. MARCA: sem </t>
+          <t>Cobertura Financeira 2022</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2021NE0000106</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>2021NE0000187</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>27/04/2021</t>
+          <t>28/06/2021</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2966</v>
+        <v>2335.68</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1339,24 +1355,24 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>115747 - (ID-115747) EXECUÇÃO DE SISTEMA DE INFORMAÇÃO, Descrição: Contratação de empresa especializada para execução de sistema de protocolo web (SPROWEB). MARCA: sem marca Termo de Contrato Nº 003/2</t>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2021NE0000107</t>
+          <t>2021NE0000186</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>27/04/2021</t>
+          <t>28/06/2021</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>7660.8</v>
+        <v>17681.14</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1365,28 +1381,28 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>116142 - (ID-116142) EXECUÇÃO DE SISTEMA DE INFORMAÇÃO, Descrição: Contratação de empresa especializada para execução do Sistema PRODAMRH - Cadastro e Folha de Pagamento de Pessoal. MARCA: sem marca T</t>
+          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e Manutenção, através da Rede Metropolitana de Manaus REPAM/MetroMao por meio de fibra ótica, incluindo o serviço d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2022NE00412</t>
+          <t>2021NE00187</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>26/2021</t>
+          <t>3/2020</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>26/10/2022</t>
+          <t>28/06/2021</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>22625.58</v>
+        <v>2335.68</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1395,28 +1411,24 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1º TA ao Contrato 026/2021 - Internet e Link</t>
+          <t>1º Termo Aditivo ao Contrato 003/2020 - SPROWEB</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2022NE0000412</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>26/2021</t>
-        </is>
-      </c>
+          <t>2025NE0000505</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>26/10/2022</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>22625.58</v>
+        <v>29778.33</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1425,24 +1437,24 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta Fundação Amazonas de Alto Rendimento -FAAR</t>
+          <t xml:space="preserve">Contratação da PRODAM Processamento de Dados Amazonas S/A, referente a prestação de serviços de METROMAO, incluindo locação de equipamentos e suporte, fornecimento de acesso gerenciado à internet por </t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2021NE0000094</t>
+          <t>2025NE0000504</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>26/04/2021</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2966</v>
+        <v>19852.22</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1451,24 +1463,28 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NOTA DE EMPENHO DE REFORÇO NR 65 EM RAZÃO DA DESCRIÇÃO ESTAR INCOMPLETA.</t>
+          <t xml:space="preserve">Contratação da PRODAM Processamento de Dados Amazonas S/A, referente a prestação de serviços de METROMAO, incluindo locação de equipamentos e suporte, fornecimento de acesso gerenciado à internet por </t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2021NE0000092</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+          <t>2025NE0000506</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>7/2025</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>26/04/2021</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17967.2</v>
+        <v>49630.55</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1477,24 +1493,24 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NOTA DE EMPENHO DE REFORÇO NR 63 EM RAZÃO DA DESCRIÇÃO ESTAR INCOMPLETA.</t>
+          <t>Contratação da PRODAM – Processamento de Dados Amazonas S/A, referente a prestação de serviços de METROMAO, incluindo locação de equipamentos e suporte, fornecimento de acesso gerenciado à internet po</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2021NE0000095</t>
+          <t>2025NE0000515</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>26/04/2021</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>7660.8</v>
+        <v>42350.56</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1503,24 +1519,28 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NOTA DE EMPENHO DE REFORÇO NR 66 EM RAZÃO DA DESCRIÇÃO ESTAR INCOMPLETA.</t>
+          <t>Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta FAAR.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2021NE0000096</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+          <t>2025NE0000512</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>9/2025</t>
+        </is>
+      </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>26/04/2021</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3401.58</v>
+        <v>5497.68</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1529,28 +1549,24 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NOTA DE EMPENHO DE REFORÇO NR 67 EM RAZÃO DA DESCRIÇÃO ESTAR INCOMPLETA.</t>
+          <t>contratação, mediante dispensa de licitação, de pessoa jurídica especializada na prestação de serviços de execução e manutenção do sistema SPROWEB.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2022NE0000551</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>26/2021</t>
-        </is>
-      </c>
+          <t>2025NE0000513</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>25/11/2022</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>22625.58</v>
+        <v>20552.68</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1559,28 +1575,28 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta Fundação Amazonas de Alto Rendimento -FAAR</t>
+          <t>Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta FAAR</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2022NE0000549</t>
+          <t>2025NE0000514</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3/2020</t>
+          <t>26/2021</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>25/11/2022</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1167.84</v>
+        <v>20552.68</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1589,28 +1605,28 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).</t>
+          <t xml:space="preserve">Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta FAAR. PARECER N. 377/2023 – ASSJUR/FAAR PARECER </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2022NE0000550</t>
+          <t>2025NE0000516</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4/2020</t>
+          <t>26/2021</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>25/11/2022</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2440</v>
+        <v>42350.56</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1619,28 +1635,24 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de disponibilização de Gestor de Conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação visual do Governo do Es</t>
+          <t xml:space="preserve">Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta FAAR. PARECER N. 377/2023 – ASSJUR/FAAR PARECER </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2022NE0000548</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2/2020</t>
-        </is>
-      </c>
+          <t>2025NE0000510</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>25/11/2022</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10146.3</v>
+        <v>1374.42</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1649,28 +1661,24 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e Manutenção, através da Rede Metropolitana de Manaus REPAM/MetroMao por meio de fibra ótica, incluindo o serviço d</t>
+          <t>Contratação, mediante dispensa de licitação, de pessoa jurídica especializada na prestação de serviços de execução e manutenção do sistema SPROWEB.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2023NE0000031</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>26/2021</t>
-        </is>
-      </c>
+          <t>2025NE0000511</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>25/01/2023</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>45251.16</v>
+        <v>4123.26</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1679,24 +1687,28 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta Fundação Amazonas de Alto Rendimento -FAAR</t>
+          <t>contratação, mediante dispensa de licitação, de pessoa jurídica especializada na prestação de serviços de execução e manutenção do sistema SPROWEB</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2023NE0000011</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>2023NE0000469</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>24/01/2023</t>
+          <t>27/10/2023</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>45251.16</v>
+        <v>1167.84</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1705,24 +1717,28 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>anulação total do empenho nº 05 de 02/01/2023 para acerto no tipo de empenho</t>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB). PARECER Nº 134/2022 – ASSJUR/FAAR TC: 003/2020 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2023NE0000001</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>2023NE0000207</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>23/01/2023</t>
+          <t>27/06/2023</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>20292.6</v>
+        <v>1169.83</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1731,28 +1747,24 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e Manutenção, através da Rede Metropolitana de Manaus REPAM/MetroMao por meio de fibra ótica, incluindo o serviço d</t>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB (SPROWEB). PARECER Nº 143/2023 – ASSJUR/FAAR TC: 0003/2020 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2023NE00202</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>4/2020</t>
-        </is>
-      </c>
+          <t>2021NE0000107</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>22/06/2023</t>
+          <t>27/04/2021</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2444.15</v>
+        <v>7660.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1761,28 +1773,24 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de hospedagem de site, compreendendo o armazenamento do site desta FAAR na infraestrutura tecnológica, para atender as necessidades desta FAAR;</t>
+          <t>116142 - (ID-116142) EXECUÇÃO DE SISTEMA DE INFORMAÇÃO, Descrição: Contratação de empresa especializada para execução do Sistema PRODAMRH - Cadastro e Folha de Pagamento de Pessoal. MARCA: sem marca T</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2023NE0000202</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>4/2020</t>
-        </is>
-      </c>
+          <t>2021NE0000106</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>22/06/2023</t>
+          <t>27/04/2021</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2444.15</v>
+        <v>2966</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1791,24 +1799,24 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de hospedagem do site, compreendendo o armazenamento do site desta FAAR na infraestrutura tecnológica, para atender as necessidades desta FAAR. PARECER</t>
+          <t>115747 - (ID-115747) EXECUÇÃO DE SISTEMA DE INFORMAÇÃO, Descrição: Contratação de empresa especializada para execução de sistema de protocolo web (SPROWEB). MARCA: sem marca Termo de Contrato Nº 003/2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2021NE0000067</t>
+          <t>2021NE0000103</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>22/04/2021</t>
+          <t>27/04/2021</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3401.58</v>
+        <v>17967.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1817,24 +1825,24 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Reforço da Notas de Empenho 2121NE0000004 Termo de Contrato Nº 004/2020; Objeto: Contratação de empresa especializada em serviços de gestão de conteúdo WEB, para publicação de informações via Website,</t>
+          <t xml:space="preserve">115752 - (ID-115752) SERVIÇO DE TRANSMISSÃO DE DADOS, Descrição: Contratação de empresa especializada para fornecimento de circuito de transmissão de dados para conexão cliente/fornecedor. MARCA: sem </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2021NE0000063</t>
+          <t>2021NE0000108</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>22/04/2021</t>
+          <t>27/04/2021</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>17967.2</v>
+        <v>3401.58</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1843,24 +1851,28 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Reforço da Notas de Empenho 2121NE0000002 Termo de Contrato Nº 002/2020; Objeto: Contratação de empresa especializada em serviços de infraestrutura de TI para acesso e manutenção através da Rede Metro</t>
+          <t xml:space="preserve">119820 - (ID-119820) HOSPEDAGEM DE SISTEMA DE INFORMAÇÃO, Descrição: Contratação de empresa especializada para prestação de serviço de hospedagem de Website, conforme Projeto Básico. MARCA: sem marca </t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2021NE0000066</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>2022NE0000412</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>26/2021</t>
+        </is>
+      </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>22/04/2021</t>
+          <t>26/10/2022</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>7660.8</v>
+        <v>22625.58</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1869,24 +1881,28 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Reforço da Notas de Empenho 2121NE0000020 Termo de Contrato Nº 003/2021; Objeto: Contratação de empresa especializada em Serviço de Execução de sistemas PRODAM-RH, para manter o cadastro dos servidore</t>
+          <t>Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta Fundação Amazonas de Alto Rendimento -FAAR</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2021NE0000065</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>2022NE00412</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>26/2021</t>
+        </is>
+      </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>22/04/2021</t>
+          <t>26/10/2022</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2966</v>
+        <v>22625.58</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1895,28 +1911,24 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Reforço da Notas de Empenho 2121NE0000003 Termo de Contrato Nº 003/2020; Objeto: Contratação de empresa especializada em serviços de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).;</t>
+          <t>1º TA ao Contrato 026/2021 - Internet e Link</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2021NE00434</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>26/2021</t>
-        </is>
-      </c>
+          <t>2021NE0000096</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>21/10/2021</t>
+          <t>26/04/2021</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>43555.02</v>
+        <v>3401.58</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1925,24 +1937,24 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Contratação de Serviços de Infraestrutura de TI para acesso e manutenção e serviço de rede.</t>
+          <t>ANULAÇÃO DA NOTA DE EMPENHO DE REFORÇO NR 67 EM RAZÃO DA DESCRIÇÃO ESTAR INCOMPLETA.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2021NE0000434</t>
+          <t>2021NE0000095</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>21/10/2021</t>
+          <t>26/04/2021</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>43555.02</v>
+        <v>7660.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1951,28 +1963,24 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM INSTALAÇÃO DE LINKS DE INTERNET, PARA QUE POSSA INTERLIGAR NOSSOS ESPAÇOS ESPORTIVOS, DE RESPONSABILIDADE DESTA FUNDAÇÃO.</t>
+          <t>ANULAÇÃO DA NOTA DE EMPENHO DE REFORÇO NR 66 EM RAZÃO DA DESCRIÇÃO ESTAR INCOMPLETA.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2022NE0000388</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>26/2021</t>
-        </is>
-      </c>
+          <t>2021NE0000092</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>21/09/2022</t>
+          <t>26/04/2021</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>41107.82</v>
+        <v>17967.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1981,28 +1989,24 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM INSTALAÇÃO DE LINKS DE INTERNET, PARA QUE POSSA INTERLIGAR NOSSOS ESPAÇOS ESPORTIVOS, DE RESPONSABILIDADE DESTA FUNDAÇÃO.</t>
+          <t>ANULAÇÃO DA NOTA DE EMPENHO DE REFORÇO NR 63 EM RAZÃO DA DESCRIÇÃO ESTAR INCOMPLETA.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2022NE0000387</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>4/2020</t>
-        </is>
-      </c>
+          <t>2021NE0000094</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>21/09/2022</t>
+          <t>26/04/2021</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4880</v>
+        <v>2966</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2011,28 +2015,28 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de disponibilização de Gestor de Conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação visual do Governo do Es</t>
+          <t>ANULAÇÃO DA NOTA DE EMPENHO DE REFORÇO NR 65 EM RAZÃO DA DESCRIÇÃO ESTAR INCOMPLETA.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2022NE0000386</t>
+          <t>2022NE0000548</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3/2020</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>21/09/2022</t>
+          <t>25/11/2022</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2335.68</v>
+        <v>10146.3</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2041,28 +2045,28 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).</t>
+          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e Manutenção, através da Rede Metropolitana de Manaus REPAM/MetroMao por meio de fibra ótica, incluindo o serviço d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2022NE0000385</t>
+          <t>2022NE0000550</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>4/2020</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>21/09/2022</t>
+          <t>25/11/2022</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>20292.6</v>
+        <v>2440</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2071,24 +2075,28 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e Manutenção, através da Rede Metropolitana de Manaus REPAM/MetroMao por meio de fibra ótica, incluindo o serviço d</t>
+          <t>Contratação de empresa especializada no serviço de disponibilização de Gestor de Conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação visual do Governo do Es</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2022NE0000384</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
+          <t>2022NE0000549</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>21/09/2022</t>
+          <t>25/11/2022</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4662.74</v>
+        <v>1167.84</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2097,28 +2105,28 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em Serviço de Execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e Folha de Pagamento de Pessoal, processar folhas de pagamento e fornecer relat</t>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2023NE00191</t>
+          <t>2022NE0000551</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>26/2021</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>20/06/2023</t>
+          <t>25/11/2022</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10631.5</v>
+        <v>22625.58</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2127,28 +2135,28 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Contratação de Empresa especializada em serviços de infraestrutura de TI para acesso e manutenção, através da Rede Metropolitana de Manaus REPAM\MetroMao por meio de fibra ótica, incluindo o serviço d</t>
+          <t>Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta Fundação Amazonas de Alto Rendimento -FAAR</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2023NE0000191</t>
+          <t>2023NE0000031</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>26/2021</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>20/06/2023</t>
+          <t>25/01/2023</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10631.5</v>
+        <v>45251.16</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2157,28 +2165,24 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e Manutenção, através da Rede Metropolitana de Manaus REPAM/MetroMao por meio de fibra ótica, incluindo o serviço d</t>
+          <t>Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta Fundação Amazonas de Alto Rendimento -FAAR</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2023NE0000100</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>3/2020</t>
-        </is>
-      </c>
+          <t>2023NE0000011</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>20/03/2023</t>
+          <t>24/01/2023</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2335.68</v>
+        <v>45251.16</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2187,28 +2191,24 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).</t>
+          <t>anulação total do empenho nº 05 de 02/01/2023 para acerto no tipo de empenho</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2023NE0000101</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>4/2020</t>
-        </is>
-      </c>
+          <t>2023NE0000001</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>20/03/2023</t>
+          <t>23/01/2023</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4880</v>
+        <v>20292.6</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2217,14 +2217,14 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de disponibilização de Gestor de Conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação visual do Governo do Es</t>
+          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e Manutenção, através da Rede Metropolitana de Manaus REPAM/MetroMao por meio de fibra ótica, incluindo o serviço d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2022NE0000210</t>
+          <t>2023NE0000202</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2234,11 +2234,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>19/05/2022</t>
+          <t>22/06/2023</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4251.98</v>
+        <v>2444.15</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2247,28 +2247,28 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de disponibilização de Gestor de Conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação visual do Governo do Es</t>
+          <t>Contratação de empresa para prestação de serviço de hospedagem do site, compreendendo o armazenamento do site desta FAAR na infraestrutura tecnológica, para atender as necessidades desta FAAR. PARECER</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2022NE0000209</t>
+          <t>2023NE00202</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3/2020</t>
+          <t>4/2020</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>19/05/2022</t>
+          <t>22/06/2023</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2335.68</v>
+        <v>2444.15</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2277,28 +2277,28 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).</t>
+          <t>Contratação de empresa para prestação de serviço de hospedagem de site, compreendendo o armazenamento do site desta FAAR na infraestrutura tecnológica, para atender as necessidades desta FAAR;</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2022NE0000208</t>
+          <t>2024NE0000107</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>26/2021</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>19/05/2022</t>
+          <t>22/04/2024</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>17681.14</v>
+        <v>39593.16</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2307,24 +2307,24 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e Manutenção, através da Rede Metropolitana de Manaus REPAM/MetroMao por meio de fibra ótica, incluindo o serviço d</t>
+          <t xml:space="preserve">Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta FAAR. PARECER N. 377/2023 – ASSJUR/FAAR PARECER </t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2022NE0000211</t>
+          <t>2021NE0000065</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>19/05/2022</t>
+          <t>22/04/2021</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>9325.48</v>
+        <v>2966</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2333,28 +2333,24 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em Serviço de Execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e Folha de Pagamento de Pessoal, processar folhas de pagamento e fornecer relat</t>
+          <t>Reforço da Notas de Empenho 2121NE0000003 Termo de Contrato Nº 003/2020; Objeto: Contratação de empresa especializada em serviços de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).;</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2021NE0000270</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>4/2020</t>
-        </is>
-      </c>
+          <t>2021NE0000066</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>17/08/2021</t>
+          <t>22/04/2021</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>8503.959999999999</v>
+        <v>7660.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2363,28 +2359,24 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1º TERMO ADITIVO OU CONTRATO Nº 004/2020, Contratação de empresa especializada em serviços de gestão de conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação </t>
+          <t>Reforço da Notas de Empenho 2121NE0000020 Termo de Contrato Nº 003/2021; Objeto: Contratação de empresa especializada em Serviço de Execução de sistemas PRODAM-RH, para manter o cadastro dos servidore</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2021NE0000269</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2/2020</t>
-        </is>
-      </c>
+          <t>2021NE0000063</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>17/08/2021</t>
+          <t>22/04/2021</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>35362.28</v>
+        <v>17967.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2393,28 +2385,24 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1º TERMO ADITIVO AO CONTRATO Nº 002/2020, contratação de empresa especializada em serviços de infraestrutura de TI para acesso e manutenção através da Rede Metropolitana de Manaus (REPAM/MEtroMao) por</t>
+          <t>Reforço da Notas de Empenho 2121NE0000002 Termo de Contrato Nº 002/2020; Objeto: Contratação de empresa especializada em serviços de infraestrutura de TI para acesso e manutenção através da Rede Metro</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2021NE0000268</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>3/2020</t>
-        </is>
-      </c>
+          <t>2021NE0000067</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>17/08/2021</t>
+          <t>22/04/2021</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4671.36</v>
+        <v>3401.58</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2423,28 +2411,24 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1º TERMO ADITIVO AO CONTRATO Nº 003/2020, Contratação de empresa especializada em serviços de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).;</t>
+          <t>Reforço da Notas de Empenho 2121NE0000004 Termo de Contrato Nº 004/2020; Objeto: Contratação de empresa especializada em serviços de gestão de conteúdo WEB, para publicação de informações via Website,</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2020NE00054</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2/2020</t>
-        </is>
-      </c>
+          <t>2021NE0000434</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>17/06/2020</t>
+          <t>21/10/2021</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>53901.6</v>
+        <v>43555.02</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2453,28 +2437,28 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Serviços de Transmissão de Dados</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM INSTALAÇÃO DE LINKS DE INTERNET, PARA QUE POSSA INTERLIGAR NOSSOS ESPAÇOS ESPORTIVOS, DE RESPONSABILIDADE DESTA FUNDAÇÃO.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2020NE00056</t>
+          <t>2021NE00434</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4/2020</t>
+          <t>26/2021</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>16/06/2020</t>
+          <t>21/10/2021</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10204.74</v>
+        <v>43555.02</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2483,28 +2467,24 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hospedagem de Sistemas - Gestor WEB</t>
+          <t>Contratação de Serviços de Infraestrutura de TI para acesso e manutenção e serviço de rede.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2020NE00055</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>3/2020</t>
-        </is>
-      </c>
+          <t>2022NE0000384</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>16/06/2020</t>
+          <t>21/09/2022</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>8898</v>
+        <v>4662.74</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2513,28 +2493,28 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Execução de sistemas - SPROWEB</t>
+          <t>Contratação de empresa especializada em Serviço de Execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e Folha de Pagamento de Pessoal, processar folhas de pagamento e fornecer relat</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2023NE00031</t>
+          <t>2022NE0000385</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>26/2021</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>15/02/2023</t>
+          <t>21/09/2022</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>45251.16</v>
+        <v>20292.6</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2543,28 +2523,28 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Cobertura Financeira</t>
+          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e Manutenção, através da Rede Metropolitana de Manaus REPAM/MetroMao por meio de fibra ótica, incluindo o serviço d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2023NE00004</t>
+          <t>2022NE0000386</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>3/2021</t>
+          <t>3/2020</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>15/02/2023</t>
+          <t>21/09/2022</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2331.37</v>
+        <v>2335.68</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2573,28 +2553,28 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Cobertura Financeira</t>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2023NE00003</t>
+          <t>2022NE0000387</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>3/2020</t>
+          <t>4/2020</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>15/02/2023</t>
+          <t>21/09/2022</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2335.68</v>
+        <v>4880</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2603,28 +2583,28 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Cobertura Financeira</t>
+          <t>Contratação de empresa especializada no serviço de disponibilização de Gestor de Conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação visual do Governo do Es</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2023NE00036</t>
+          <t>2022NE0000388</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>26/2021</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>15/02/2023</t>
+          <t>21/09/2022</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2292.6</v>
+        <v>41107.82</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2633,14 +2613,14 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cobertura Financeira</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM INSTALAÇÃO DE LINKS DE INTERNET, PARA QUE POSSA INTERLIGAR NOSSOS ESPAÇOS ESPORTIVOS, DE RESPONSABILIDADE DESTA FUNDAÇÃO.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2023NE0000036</t>
+          <t>2024NE0000080</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2650,11 +2630,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>15/02/2023</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>20292.6</v>
+        <v>18603.6</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2663,14 +2643,14 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e Manutenção, através da Rede Metropolitana de Manaus REPAM/MetroMao por meio de fibra ótica, incluindo o serviço d</t>
+          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e manutenção, através da Rede Metropolitana de Manaus através de fibra ótica, incluindo o serviço de Acesso à Inter</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2022NE0000426</t>
+          <t>2023NE0000191</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2680,11 +2660,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>08/11/2022</t>
+          <t>20/06/2023</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10146.3</v>
+        <v>10631.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2700,21 +2680,21 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2022NE0000424</t>
+          <t>2023NE00191</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>4/2020</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>08/11/2022</t>
+          <t>20/06/2023</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2440</v>
+        <v>10631.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2723,28 +2703,28 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de disponibilização de Gestor de Conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação visual do Governo do Es</t>
+          <t>Contratação de Empresa especializada em serviços de infraestrutura de TI para acesso e manutenção, através da Rede Metropolitana de Manaus REPAM\MetroMao por meio de fibra ótica, incluindo o serviço d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2022NE0000425</t>
+          <t>2023NE0000101</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3/2020</t>
+          <t>4/2020</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>08/11/2022</t>
+          <t>20/03/2023</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1167.84</v>
+        <v>4880</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2753,24 +2733,28 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).</t>
+          <t>Contratação de empresa especializada no serviço de disponibilização de Gestor de Conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação visual do Governo do Es</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2021NE0000407</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
+          <t>2023NE0000100</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>08/10/2021</t>
+          <t>20/03/2023</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>7660.8</v>
+        <v>2335.68</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2779,28 +2763,28 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Termo de Contrato Nº 003/2021; Objeto: Contratação de empresa especializada em Serviço de Execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e Folha de Pagamento de Pessoal, process</t>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2023NE0000519</t>
+          <t>2024NE0000205</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>4/2020</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>07/11/2023</t>
+          <t>19/06/2024</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2444.15</v>
+        <v>9301.799999999999</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2809,28 +2793,24 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de hospedagem do site, compreendendo o armazenamento do site desta FAAR na infraestrutura tecnológica, para atender as necessidades desta FAAR. PARECER</t>
+          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e manutenção, através da Rede Metropolitana de Manaus através de fibra ótica, incluindo o serviço de Acesso à Inter</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2023NE0000212</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>4/2020</t>
-        </is>
-      </c>
+          <t>2022NE0000211</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>05/07/2023</t>
+          <t>19/05/2022</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2440</v>
+        <v>9325.48</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2839,14 +2819,14 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de disponibilização de Gestor de Conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação visual do Governo do Es</t>
+          <t>Contratação de empresa especializada em Serviço de Execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e Folha de Pagamento de Pessoal, processar folhas de pagamento e fornecer relat</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2023NE0000210</t>
+          <t>2022NE0000208</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2856,11 +2836,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>05/07/2023</t>
+          <t>19/05/2022</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10146.3</v>
+        <v>17681.14</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2869,14 +2849,14 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e Manutenção, através da Rede Metropolitana de Manaus REPAM/MetroMao, incluindo o serviço de Acesso à Internet atra</t>
+          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e Manutenção, através da Rede Metropolitana de Manaus REPAM/MetroMao por meio de fibra ótica, incluindo o serviço d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2023NE0000211</t>
+          <t>2022NE0000209</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2886,11 +2866,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>05/07/2023</t>
+          <t>19/05/2022</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1167.84</v>
+        <v>2335.68</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2899,28 +2879,28 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB). PARECER Nº 134/2022 – ASSJUR/FAAR TC: 003/2020 AD: 02.</t>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2022NE00032</t>
+          <t>2022NE0000210</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>3/2021</t>
+          <t>4/2020</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>05/01/2022</t>
+          <t>19/05/2022</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6994.11</v>
+        <v>4251.98</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2929,24 +2909,28 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1º T.A Contrato 003/2021 - Prazo e Reaj. 21,73%</t>
+          <t>Contratação de empresa especializada no serviço de disponibilização de Gestor de Conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação visual do Governo do Es</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2022NE0000032</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
+          <t>2021NE0000268</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>05/01/2022</t>
+          <t>17/08/2021</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>6994.11</v>
+        <v>4671.36</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2955,28 +2939,28 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em Serviço de Execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e Folha de Pagamento de Pessoal, processar folhas de pagamento e fornecer relat</t>
+          <t>1º TERMO ADITIVO AO CONTRATO Nº 003/2020, Contratação de empresa especializada em serviços de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).;</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2021NE0000003</t>
+          <t>2021NE0000269</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>3/2020</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>04/01/2021</t>
+          <t>17/08/2021</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>5932</v>
+        <v>35362.28</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2985,14 +2969,14 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).</t>
+          <t>1º TERMO ADITIVO AO CONTRATO Nº 002/2020, contratação de empresa especializada em serviços de infraestrutura de TI para acesso e manutenção através da Rede Metropolitana de Manaus (REPAM/MEtroMao) por</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2021NE0000004</t>
+          <t>2021NE0000270</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3002,11 +2986,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>04/01/2021</t>
+          <t>17/08/2021</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>6803.16</v>
+        <v>8503.959999999999</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3015,14 +2999,14 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de disponibilização de Gestor de Conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação visual do Governo do Es</t>
+          <t xml:space="preserve">1º TERMO ADITIVO OU CONTRATO Nº 004/2020, Contratação de empresa especializada em serviços de gestão de conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação </t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2021NE0000002</t>
+          <t>2020NE00054</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3032,11 +3016,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>04/01/2021</t>
+          <t>17/06/2020</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>35934.4</v>
+        <v>53901.6</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3045,28 +3029,24 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e Manutenção, através da Rede Metropolitana de Manaus REPAM/MetroMao por meio de fibra ótica, incluindo o serviço d</t>
+          <t>Serviços de Transmissão de Dados</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2022NE0000010</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>3/2020</t>
-        </is>
-      </c>
+          <t>2025NE0000587</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>03/01/2022</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>4671.36</v>
+        <v>9926.110000000001</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3075,28 +3055,28 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).</t>
+          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO N° 2025NE0000506 EM VIRTUDE DO DECRETO N° 52.770 DE 21/10/2025 ENCERRAMENTO DA EXECUÇÃO ORÇAMENTARIA, FINANCEIRA, PATRIMONIAL E CONTABIL DO EXERCICIO DE 2025</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2022NE0000012</t>
+          <t>2025NE0000322</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>4/2020</t>
+          <t>26/2021</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>03/01/2022</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>8503.959999999999</v>
+        <v>42350.56</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3105,28 +3085,24 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de disponibilização de Gestor de Conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação visual do Governo do Es</t>
+          <t xml:space="preserve">Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta FAAR. PARECER N. 377/2023 – ASSJUR/FAAR PARECER </t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2022NE0000023</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2/2020</t>
-        </is>
-      </c>
+          <t>2025NE0000320</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>03/01/2022</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>35362.28</v>
+        <v>29778.33</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3135,24 +3111,28 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e Manutenção, através da Rede Metropolitana de Manaus REPAM/MetroMao por meio de fibra ótica, incluindo o serviço d</t>
+          <t>CANCELA NOTA DE EMPENHO Nº 2025NE0000315, PARA CORREÇÃO DE FONTE.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2022NE0000031</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>2025NE0000321</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>7/2025</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>03/01/2022</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1915.2</v>
+        <v>29778.33</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3161,28 +3141,28 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em Serviço de Execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e Folha de Pagamento de Pessoal, processar folhas de pagamento e fornecer relat</t>
+          <t>Contratação da PRODAM – Processamento de Dados Amazonas S/A, referente a prestação de serviços de METROMAO, incluindo locação de equipamentos e suporte, fornecimento de acesso gerenciado à internet po</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2023NE0000009</t>
+          <t>2020NE00055</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>4/2020</t>
+          <t>3/2020</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>02/01/2023</t>
+          <t>16/06/2020</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>4880</v>
+        <v>8898</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3191,24 +3171,28 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de disponibilização de Gestor de Conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação visual do Governo do Es</t>
+          <t>Execução de sistemas - SPROWEB</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2023NE0000004</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>2020NE00056</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>4/2020</t>
+        </is>
+      </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>02/01/2023</t>
+          <t>16/06/2020</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2331.37</v>
+        <v>10204.74</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3217,28 +3201,28 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em Serviço de Execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e Folha de Pagamento de Pessoal, processar folhas de pagamento e fornecer relat</t>
+          <t>Hospedagem de Sistemas - Gestor WEB</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2023NE0000003</t>
+          <t>2025NE0000150</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>3/2020</t>
+          <t>26/2021</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>02/01/2023</t>
+          <t>16/05/2025</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2335.68</v>
+        <v>41105.36</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3247,24 +3231,28 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).</t>
+          <t xml:space="preserve">Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta FAAR. PARECER N. 377/2023 – ASSJUR/FAAR PARECER </t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2023NE0000008</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
+          <t>2025NE0000147</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2/2020</t>
+        </is>
+      </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>02/01/2023</t>
+          <t>16/05/2025</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>20292.6</v>
+        <v>18603.6</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3273,28 +3261,28 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Anulação total da NE 2023NE0000001, por motivo de data e modalidade informada errada</t>
+          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e manutenção, através da Rede Metropolitana de Manaus através de fibra ótica, incluindo o serviço de Acesso à Inter</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2023NE0000005</t>
+          <t>2025NE0000149</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>26/2021</t>
+          <t>4/2020</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>02/01/2023</t>
+          <t>16/05/2025</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>45251.16</v>
+        <v>4888.3</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3303,35 +3291,1845 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta Fundação Amazonas de Alto Rendimento -FAAR</t>
+          <t>Contratação de empresa para prestação de serviço de hospedagem do site, compreendendo o armazenamento do site desta FAAR na infraestrutura tecnológica, para atender as necessidades desta FAAR. PARECER</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>2025NE0000148</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>16/05/2025</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>2339.66</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB (SPROWEB). PARECER Nº 143/2023 – ASSJUR/FAAR TC: 0003/2020 AD: 05.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2025NE0000319</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>9/2025</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>4123.26</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>contratação, mediante dispensa de licitação, de pessoa jurídica especializada na prestação de serviços de execução e manutenção do sistema SPROWEB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2024NE0000332</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>15/10/2024</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>3509.49</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB (SPROWEB). PARECER Nº 143/2023 – ASSJUR/FAAR TC: 0003/2020 AD: 05.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2024NE0000333</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>4/2020</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>15/10/2024</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>7332.45</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Contratação de empresa para prestação de serviço de hospedagem do site, compreendendo o armazenamento do site desta FAAR na infraestrutura tecnológica, para atender as necessidades desta FAAR. PARECER</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2024NE0000331</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2/2020</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>15/10/2024</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>27905.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e manutenção, através da Rede Metropolitana de Manaus através de fibra ótica, incluindo o serviço de Acesso à Inter</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2023NE0000036</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2/2020</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>15/02/2023</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>20292.6</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e Manutenção, através da Rede Metropolitana de Manaus REPAM/MetroMao por meio de fibra ótica, incluindo o serviço d</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2023NE00036</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2/2020</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>15/02/2023</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>2292.6</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Cobertura Financeira</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2023NE00003</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>15/02/2023</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>2335.68</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Cobertura Financeira</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2023NE00004</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>3/2021</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>15/02/2023</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>2331.37</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Cobertura Financeira</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2023NE00031</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>26/2021</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>15/02/2023</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>45251.16</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Cobertura Financeira</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2025NE0000315</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>7/2025</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>14/10/2025</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>29778.33</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Contratação da PRODAM – Processamento de Dados Amazonas S/A, referente a prestação de serviços de METROMAO, incluindo locação de equipamentos e suporte, fornecimento de acesso gerenciado à internet po</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2025NE0000054</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2/2020</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>13/03/2025</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>18603.6</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e manutenção, através da Rede Metropolitana de Manaus através de fibra ótica, incluindo o serviço de Acesso à Inter</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2025NE0000055</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>13/03/2025</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>2339.66</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB (SPROWEB). PARECER Nº 143/2023 – ASSJUR/FAAR TC: 0003/2020 AD: 05.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2025NE0000056</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>4/2020</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>13/03/2025</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>4888.3</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Contratação de empresa para prestação de serviço de hospedagem do site, compreendendo o armazenamento do site desta FAAR na infraestrutura tecnológica, para atender as necessidades desta FAAR. PARECER</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2025NE0000057</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>26/2021</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>13/03/2025</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>41105.36</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta FAAR. PARECER N. 377/2023 – ASSJUR/FAAR PARECER </t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2025NE0000278</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>9/2025</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>12/09/2025</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1374.42</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>contratação, mediante dispensa de licitação, de pessoa jurídica especializada na prestação de serviços de execução e manutenção do sistema SPROWEB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2025NE0000277</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>26/2021</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>12/09/2025</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>20552.68</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta FAAR. PARECER N. 377/2023 – ASSJUR/FAAR PARECER </t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2025NE0000279</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>10/2025</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>12/09/2025</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>2784.24</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização de gestor de conteúdo web.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2024NE0000296</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>11/09/2024</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>2339.66</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB (SPROWEB). PARECER Nº 143/2023 – ASSJUR/FAAR TC: 0003/2020 AD: 05.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2025NE0000312</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>10/2025</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>8352.719999999999</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização de gestor de conteúdo web.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2022NE0000425</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>08/11/2022</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1167.84</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2022NE0000424</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>4/2020</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>08/11/2022</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>2440</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada no serviço de disponibilização de Gestor de Conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação visual do Governo do Es</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2022NE0000426</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2/2020</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>08/11/2022</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10146.3</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e Manutenção, através da Rede Metropolitana de Manaus REPAM/MetroMao por meio de fibra ótica, incluindo o serviço d</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2021NE0000407</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>08/10/2021</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>7660.8</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Termo de Contrato Nº 003/2021; Objeto: Contratação de empresa especializada em Serviço de Execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e Folha de Pagamento de Pessoal, process</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2023NE0000519</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>4/2020</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>07/11/2023</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>2444.15</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Contratação de empresa para prestação de serviço de hospedagem do site, compreendendo o armazenamento do site desta FAAR na infraestrutura tecnológica, para atender as necessidades desta FAAR. PARECER</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2024NE0000061</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>4/2020</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>07/03/2024</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>4888.3</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Contratação de empresa para prestação de serviço de hospedagem do site, compreendendo o armazenamento do site desta FAAR na infraestrutura tecnológica, para atender as necessidades desta FAAR. PARECER</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2024NE0000192</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>4/2020</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>06/06/2024</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>2444.15</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Contratação de empresa para prestação de serviço de hospedagem do site, compreendendo o armazenamento do site desta FAAR na infraestrutura tecnológica, para atender as necessidades desta FAAR. PARECER</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2024NE0000195</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>26/2021</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>06/06/2024</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>39593.16</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta FAAR. PARECER N. 377/2023 – ASSJUR/FAAR PARECER </t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2024NE0000191</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>4/2020</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>06/06/2024</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>4888.3</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Contratação de empresa para prestação de serviço de hospedagem do site, compreendendo o armazenamento do site desta FAAR na infraestrutura tecnológica, para atender as necessidades desta FAAR. PARECER</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2023NE0000211</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>05/07/2023</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1167.84</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB). PARECER Nº 134/2022 – ASSJUR/FAAR TC: 003/2020 AD: 02.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2023NE0000210</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2/2020</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>05/07/2023</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10146.3</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e Manutenção, através da Rede Metropolitana de Manaus REPAM/MetroMao, incluindo o serviço de Acesso à Internet atra</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2023NE0000212</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>4/2020</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>05/07/2023</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>2440</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada no serviço de disponibilização de Gestor de Conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação visual do Governo do Es</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2024NE0000058</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>05/03/2024</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>2339.66</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB (SPROWEB). PARECER Nº 143/2023 – ASSJUR/FAAR TC: 0003/2020 AD: 04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026NE0000003</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>26/2021</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>84701.12</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta FAAR. PARECER N. 377/2023 – ASSJUR/FAAR PARECER </t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026NE0000006</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>10/2025</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>11136.96</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização de gestor de conteúdo web.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026NE0000005</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>9/2025</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>5497.68</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>contratação, mediante dispensa de licitação, de pessoa jurídica especializada na prestação de serviços de execução e manutenção do sistema SPROWEB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2022NE0000032</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>05/01/2022</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>6994.11</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada em Serviço de Execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e Folha de Pagamento de Pessoal, processar folhas de pagamento e fornecer relat</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2022NE00032</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>3/2021</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>05/01/2022</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>6994.11</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1º T.A Contrato 003/2021 - Prazo e Reaj. 21,73%</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2024NE0000189</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>04/06/2024</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1169.83</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB (SPROWEB). PARECER Nº 143/2023 – ASSJUR/FAAR TC: 0003/2020 AD: 05.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2024NE0000187</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2/2020</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>04/06/2024</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>18603.6</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e manutenção, através da Rede Metropolitana de Manaus através de fibra ótica, incluindo o serviço de Acesso à Inter</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2024NE0000188</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>04/06/2024</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>2339.66</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB (SPROWEB). PARECER Nº 143/2023 – ASSJUR/FAAR TC: 0003/2020 AD: 04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2021NE0000002</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2/2020</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>04/01/2021</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>35934.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e Manutenção, através da Rede Metropolitana de Manaus REPAM/MetroMao por meio de fibra ótica, incluindo o serviço d</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2021NE0000004</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>4/2020</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>04/01/2021</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>6803.16</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada no serviço de disponibilização de Gestor de Conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação visual do Governo do Es</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2021NE0000003</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>04/01/2021</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>5932</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2022NE0000031</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>03/01/2022</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1915.2</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada em Serviço de Execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e Folha de Pagamento de Pessoal, processar folhas de pagamento e fornecer relat</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2022NE0000023</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2/2020</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>03/01/2022</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>35362.28</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e Manutenção, através da Rede Metropolitana de Manaus REPAM/MetroMao por meio de fibra ótica, incluindo o serviço d</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2022NE0000012</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>4/2020</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>03/01/2022</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>8503.959999999999</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada no serviço de disponibilização de Gestor de Conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação visual do Governo do Es</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2022NE0000010</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>03/01/2022</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>4671.36</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2025NE0000003</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>02/01/2025</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>2339.66</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB (SPROWEB). PARECER Nº 143/2023 – ASSJUR/FAAR TC: 0003/2020 AD: 05.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2025NE0000034</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>26/2021</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>02/01/2025</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>41105.36</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta FAAR. PARECER N. 377/2023 – ASSJUR/FAAR PARECER </t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2025NE0000004</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>4/2020</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>02/01/2025</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>4888.3</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Contratação de empresa para prestação de serviço de hospedagem do site, compreendendo o armazenamento do site desta FAAR na infraestrutura tecnológica, para atender as necessidades desta FAAR. PARECER</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2023NE0000005</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>26/2021</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>02/01/2023</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>45251.16</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta Fundação Amazonas de Alto Rendimento -FAAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2023NE0000008</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>02/01/2023</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>20292.6</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Anulação total da NE 2023NE0000001, por motivo de data e modalidade informada errada</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2023NE0000003</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>02/01/2023</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>2335.68</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB. (SPROWEB).</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2023NE0000004</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>02/01/2023</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>2331.37</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada em Serviço de Execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e Folha de Pagamento de Pessoal, processar folhas de pagamento e fornecer relat</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2023NE0000009</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>4/2020</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>02/01/2023</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>4880</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada no serviço de disponibilização de Gestor de Conteúdo WEB, para publicação de informações via Website, de acordo com o padrão de comunicação visual do Governo do Es</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2025NE0000302</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>26/2021</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>20552.68</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta FAAR. PARECER N. 377/2023 – ASSJUR/FAAR PARECER </t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2024NE0000019</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2/2020</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>01/02/2024</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>18603.6</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada em serviços de Infraestrutura de TI para acesso e manutenção, através da Rede Metropolitana de Manaus através de fibra ótica, incluindo o serviço de Acesso à Inter</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2024NE0000021</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>26/2021</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>01/02/2024</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>39593.16</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contratação de empresa especializada em instalação de links de internet, para que possa interligar nossos espaços esportivos de responsabilidades desta FAAR. PARECER N. 377/2023 – ASSJUR/FAAR PARECER </t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2024NE0000020</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>4/2020</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>01/02/2024</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>4888.3</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Contratação de empresa para prestação de serviço de hospedagem do site, compreendendo o armazenamento do site desta FAAR na infraestrutura tecnológica, para atender as necessidades desta FAAR. PARECER</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2024NE0000022</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>01/02/2024</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>2339.66</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Contratação de empresa especializada no serviço de execução de Sistema de Protocolo em plataforma WEB (SPROWEB). PARECER Nº 143/2023 – ASSJUR/FAAR TC: 0003/2020 AD: 04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
           <t>2021NE00020</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>3/2021</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C156" t="inlineStr">
         <is>
           <t>01/01/2021</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="D156" t="n">
         <v>5745.6</v>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
         <is>
           <t>Serviço de Execução de PRODAM RH</t>
         </is>
@@ -3348,7 +5146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4080,26 +5878,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>139492</t>
+          <t>164363</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>35977</t>
+          <t>59161</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>26/2021</t>
+          <t>358/2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>03/2023</t>
+          <t>07/2025</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5896.83</v>
+        <v>6500</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4112,32 +5910,32 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>140173</t>
+          <t>164365</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>37129</t>
+          <t>59165</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>26/2021</t>
+          <t>358/2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>04/2023</t>
+          <t>08/2025</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5896.83</v>
+        <v>6500</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4150,18 +5948,18 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>140909</t>
+          <t>162783</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>37341</t>
+          <t>57831</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4171,11 +5969,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>05/2023</t>
+          <t>09/2025</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5896.83</v>
+        <v>6122.1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4194,12 +5992,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>141652</t>
+          <t>139492</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>38357</t>
+          <t>35977</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4209,7 +6007,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>06/2023</t>
+          <t>03/2023</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -4232,12 +6030,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>142390</t>
+          <t>140173</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>37129</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4247,7 +6045,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>07/2023</t>
+          <t>04/2023</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -4270,12 +6068,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>143188</t>
+          <t>140909</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>39397</t>
+          <t>37341</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4285,7 +6083,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>08/2023</t>
+          <t>05/2023</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -4308,12 +6106,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>143948</t>
+          <t>141652</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>40256</t>
+          <t>38357</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4323,7 +6121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>09/2023</t>
+          <t>06/2023</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -4346,12 +6144,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>144722</t>
+          <t>142390</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>41064</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4361,7 +6159,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>07/2023</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -4384,12 +6182,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>145871</t>
+          <t>143188</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>41771</t>
+          <t>39397</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4399,7 +6197,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>08/2023</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -4422,12 +6220,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>146169</t>
+          <t>143948</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>42206</t>
+          <t>40256</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4437,7 +6235,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>09/2023</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -4450,7 +6248,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>FORTE</t>
+          <t>COMPLETA</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -4460,12 +6258,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>139493</t>
+          <t>144722</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>35976</t>
+          <t>41064</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4475,11 +6273,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>03/2023</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2711.55</v>
+        <v>5896.83</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4498,12 +6296,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>140174</t>
+          <t>145871</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>36648</t>
+          <t>41771</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4513,11 +6311,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>04/2023</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2711.55</v>
+        <v>5896.83</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4536,12 +6334,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>140910</t>
+          <t>146169</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>37342</t>
+          <t>42206</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4551,11 +6349,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>05/2023</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2711.55</v>
+        <v>5896.83</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4564,7 +6362,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>COMPLETA</t>
+          <t>FORTE</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -4574,26 +6372,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>141653</t>
+          <t>164364</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>38358</t>
+          <t>59162</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>26/2021</t>
+          <t>358/2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>06/2023</t>
+          <t>07/2025</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2711.55</v>
+        <v>3426.11</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4606,32 +6404,32 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>142391</t>
+          <t>164366</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>38703</t>
+          <t>59164</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>26/2021</t>
+          <t>358/2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>07/2023</t>
+          <t>08/2025</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2711.55</v>
+        <v>3426.11</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4644,32 +6442,32 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>143189</t>
+          <t>164102</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>39396</t>
+          <t>59052</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>26/2021</t>
+          <t>356/2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>08/2023</t>
+          <t>08/2025</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2711.55</v>
+        <v>2784.24</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4682,32 +6480,32 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>143949</t>
+          <t>164101</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>40255</t>
+          <t>59053</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>26/2021</t>
+          <t>356/2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>09/2023</t>
+          <t>07/2025</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2711.55</v>
+        <v>2784.24</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4716,22 +6514,22 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>FORTE</t>
+          <t>COMPLETA</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>144723</t>
+          <t>139493</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>41065</t>
+          <t>35976</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4741,7 +6539,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>03/2023</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4764,12 +6562,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>145872</t>
+          <t>140174</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>41770</t>
+          <t>36648</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4779,7 +6577,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>04/2023</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4802,12 +6600,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>146170</t>
+          <t>140910</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>42207</t>
+          <t>37342</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4817,7 +6615,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>05/2023</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4830,7 +6628,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>FORTE</t>
+          <t>COMPLETA</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -4840,26 +6638,26 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>143184</t>
+          <t>141653</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>39394</t>
+          <t>38358</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>26/2021</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>08/2023</t>
+          <t>06/2023</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2681.1</v>
+        <v>2711.55</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4872,32 +6670,32 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>127</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>143944</t>
+          <t>142391</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>40253</t>
+          <t>38703</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>26/2021</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>09/2023</t>
+          <t>07/2023</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2681.1</v>
+        <v>2711.55</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4906,36 +6704,36 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>FORTE</t>
+          <t>COMPLETA</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>127</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>144718</t>
+          <t>143189</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>41062</t>
+          <t>39396</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>26/2021</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>08/2023</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2681.1</v>
+        <v>2711.55</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4948,32 +6746,32 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>127</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>145407</t>
+          <t>143949</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>41454</t>
+          <t>40255</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>26/2021</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>09/2023</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2681.1</v>
+        <v>2711.55</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4982,36 +6780,36 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>COMPLETA</t>
+          <t>FORTE</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>127</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>146166</t>
+          <t>144723</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>42204</t>
+          <t>41065</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>26/2021</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2681.1</v>
+        <v>2711.55</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5020,36 +6818,36 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>FORTE</t>
+          <t>COMPLETA</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>127</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>140168</t>
+          <t>145872</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>37128</t>
+          <t>41770</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>26/2021</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>04/2023</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2676.54</v>
+        <v>2711.55</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5062,32 +6860,32 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>127</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>140904</t>
+          <t>146170</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>37339</t>
+          <t>42207</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>26/2021</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>05/2023</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2676.54</v>
+        <v>2711.55</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5100,18 +6898,18 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>127</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>141647</t>
+          <t>143184</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>38355</t>
+          <t>39394</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5121,11 +6919,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>06/2023</t>
+          <t>08/2023</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2676.54</v>
+        <v>2681.1</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5144,26 +6942,26 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>143186</t>
+          <t>143944</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>39395</t>
+          <t>40253</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>4/2020</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>08/2023</t>
+          <t>09/2023</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2444.15</v>
+        <v>2681.1</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5172,36 +6970,36 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>COMPLETA</t>
+          <t>FORTE</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>143946</t>
+          <t>144718</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>40254</t>
+          <t>41062</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>4/2020</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>09/2023</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2444.15</v>
+        <v>2681.1</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5210,36 +7008,36 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>FORTE</t>
+          <t>COMPLETA</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>144720</t>
+          <t>145407</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>41063</t>
+          <t>41454</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>4/2020</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2444.15</v>
+        <v>2681.1</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5252,32 +7050,32 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>145409</t>
+          <t>146166</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>41455</t>
+          <t>42204</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>4/2020</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2444.15</v>
+        <v>2681.1</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5286,36 +7084,36 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>COMPLETA</t>
+          <t>FORTE</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>146168</t>
+          <t>140168</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>42205</t>
+          <t>37128</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>4/2020</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>04/2023</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2444.15</v>
+        <v>2676.54</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5324,36 +7122,36 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>FORTE</t>
+          <t>COMPLETA</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>141650</t>
+          <t>140904</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>38356</t>
+          <t>37339</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>4/2020</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>06/2023</t>
+          <t>05/2023</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2440</v>
+        <v>2676.54</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5362,36 +7160,36 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>COMPLETA</t>
+          <t>FORTE</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>141368</t>
+          <t>141647</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>37758</t>
+          <t>38355</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>26/2023</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>05/2023</t>
+          <t>06/2023</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2146.36</v>
+        <v>2676.54</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5404,32 +7202,32 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>140002</t>
+          <t>143186</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>36491</t>
+          <t>39395</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>26/2023</t>
+          <t>4/2020</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>03/2023</t>
+          <t>08/2023</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1216.67</v>
+        <v>2444.15</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5442,32 +7240,32 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>76</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>140718</t>
+          <t>143946</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>37120</t>
+          <t>40254</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>26/2023</t>
+          <t>4/2020</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>04/2023</t>
+          <t>09/2023</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1211.73</v>
+        <v>2444.15</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5476,40 +7274,40 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>COMPLETA</t>
+          <t>FORTE</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>76</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>140170</t>
+          <t>144720</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>36646</t>
+          <t>41063</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3/2020</t>
+          <t>4/2020</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>04/2023</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1167.84</v>
+        <v>2444.15</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Parcialmente Paga</t>
+          <t>Emitida</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5518,32 +7316,32 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>142183</t>
+          <t>145409</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>38453</t>
+          <t>41455</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>26/2023</t>
+          <t>4/2020</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>06/2023</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1032.77</v>
+        <v>2444.15</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5556,32 +7354,32 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>76</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>145882</t>
+          <t>146168</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>41781</t>
+          <t>42205</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>26/2023</t>
+          <t>4/2020</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1011.63</v>
+        <v>2444.15</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5594,32 +7392,32 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>76</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>144445</t>
+          <t>141650</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>40508</t>
+          <t>38356</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>26/2023</t>
+          <t>4/2020</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>09/2023</t>
+          <t>06/2023</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1011.21</v>
+        <v>2440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5632,18 +7430,18 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>76</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>140001</t>
+          <t>141368</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>36492</t>
+          <t>37758</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5653,11 +7451,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>02/2023</t>
+          <t>05/2023</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1009.43</v>
+        <v>2146.36</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5666,7 +7464,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>FORTE</t>
+          <t>COMPLETA</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -5676,26 +7474,26 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>143742</t>
+          <t>164361</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>39870</t>
+          <t>59160</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>26/2023</t>
+          <t>357/2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>08/2023</t>
+          <t>07/2025</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1006.21</v>
+        <v>1374.42</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5714,26 +7512,26 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>145197</t>
+          <t>164362</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>41169</t>
+          <t>59163</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>26/2023</t>
+          <t>357/2025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>08/2025</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1001.81</v>
+        <v>1374.42</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5752,38 +7550,380 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>140002</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>36491</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>26/2023</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>03/2023</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1216.67</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>COMPLETA</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>140718</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>37120</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>26/2023</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>04/2023</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1211.73</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>COMPLETA</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>140170</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>36646</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>04/2023</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1167.84</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Parcialmente Paga</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>COMPLETA</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>142183</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>38453</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>26/2023</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>06/2023</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1032.77</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>COMPLETA</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>145882</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>41781</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>26/2023</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>11/2023</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1011.63</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>FORTE</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>144445</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>40508</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>26/2023</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>09/2023</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1011.21</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>COMPLETA</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>140001</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>36492</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>26/2023</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>02/2023</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1009.43</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>FORTE</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>143742</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>39870</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>26/2023</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>08/2023</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1006.21</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>COMPLETA</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>145197</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>41169</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>26/2023</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>10/2023</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1001.81</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>COMPLETA</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>142946</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>39165</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>26/2023</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>07/2023</t>
         </is>
       </c>
-      <c r="E64" t="n">
+      <c r="E73" t="n">
         <v>999.89</v>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Emitida</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>FORTE</t>
         </is>
       </c>
-      <c r="H64" t="n">
+      <c r="H73" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5798,7 +7938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9129,6 +11269,474 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SEDEL</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Fornecimento de circuito de transmissão de dados</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>026/2021</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>162783</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>09/2025</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>6.122,10</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>171 dias</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SEDEL</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Licença de uso de sistemas de informação</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>356/2025</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>164102</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>08/2025</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2.784,24</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>119 dias</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SEDEL</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Licença de uso de sistemas de informação</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>356/2025</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>164101</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>07/2025</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2.784,24</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>119 dias</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SEDEL</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>357/2025</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>164361</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>07/2025</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1.374,42</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>115 dias</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SEDEL</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Acesso Gerenciado à Rede Mundial</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>358/2025</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>164363</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>07/2025</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>6.500,00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>115 dias</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SEDEL</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Acesso à MetroMao</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>358/2025</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>164364</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>07/2025</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>3.426,11</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>115 dias</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SEDEL</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>357/2025</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>164362</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>08/2025</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1.374,42</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>115 dias</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SEDEL</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Acesso à MetroMao</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>358/2025</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>164366</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>08/2025</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>3.426,11</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>115 dias</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SEDEL</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Acesso Gerenciado à Rede Mundial</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>358/2025</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>164365</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>08/2025</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>6.500,00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>115 dias</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/DOSSIES_MULTIFORMATO/FAAR_SEDEL/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/FAAR_SEDEL/dossie.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2028-03-31</t>
         </is>
       </c>
     </row>
